--- a/output/tables/GD/finished tables/Temp2_Global_Fst.xlsx
+++ b/output/tables/GD/finished tables/Temp2_Global_Fst.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\revised_bison_popgen\output\tables\GD\finished tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\revised_bison_popgen\output\tables\GD\finished tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2FFB18-CACD-4FF3-8A06-FFD87F39C68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{C3156F88-7FD5-453A-A002-53DDAA4F8AD3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3156F88-7FD5-453A-A002-53DDAA4F8AD3}"/>
   </bookViews>
   <sheets>
     <sheet name="fst2" sheetId="1" r:id="rId1"/>
@@ -1034,12 +1034,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F44852F6-A395-487A-89DF-6A5E0A6BD1B1}">
   <dimension ref="A1:T21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.05" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>19</v>
       </c>
@@ -1065,7 +1065,7 @@
       <c r="S1" s="1"/>
       <c r="T1"/>
     </row>
-    <row r="2" spans="1:20" ht="15.05" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="B2" s="4" t="s">
         <v>12</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="T2"/>
     </row>
-    <row r="3" spans="1:20" ht="15.05" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -1137,7 +1137,7 @@
       <c r="I3" s="5"/>
       <c r="T3"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -1162,7 +1162,7 @@
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -1189,7 +1189,7 @@
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
@@ -1218,7 +1218,7 @@
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
@@ -1249,7 +1249,7 @@
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>0</v>
       </c>
@@ -1282,7 +1282,7 @@
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>17</v>
       </c>
@@ -1317,7 +1317,7 @@
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
@@ -1354,7 +1354,7 @@
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
@@ -1393,7 +1393,7 @@
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
@@ -1434,7 +1434,7 @@
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
@@ -1477,7 +1477,7 @@
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
@@ -1522,7 +1522,7 @@
       <c r="R14" s="10"/>
       <c r="S14" s="10"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -1618,7 +1618,7 @@
       <c r="R16" s="10"/>
       <c r="S16" s="10"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -1669,7 +1669,7 @@
       <c r="R17" s="10"/>
       <c r="S17" s="10"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>8</v>
       </c>
@@ -1722,7 +1722,7 @@
       <c r="R18" s="10"/>
       <c r="S18" s="10"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -1777,7 +1777,7 @@
       <c r="R19" s="10"/>
       <c r="S19" s="10"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>10</v>
       </c>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S20" s="10"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>11</v>
       </c>

--- a/output/tables/GD/finished tables/Temp2_Global_Fst.xlsx
+++ b/output/tables/GD/finished tables/Temp2_Global_Fst.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\revised_bison_popgen\output\tables\GD\finished tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\revised_bison_popgen\output\tables\GD\finished tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2FFB18-CACD-4FF3-8A06-FFD87F39C68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39D187C-8A66-4D61-96CE-DEBDCFB30D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3156F88-7FD5-453A-A002-53DDAA4F8AD3}"/>
+    <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{C3156F88-7FD5-453A-A002-53DDAA4F8AD3}"/>
   </bookViews>
   <sheets>
     <sheet name="fst2" sheetId="1" r:id="rId1"/>
@@ -73,12 +73,6 @@
     <t>PAD</t>
   </si>
   <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
     <t>Herd</t>
   </si>
   <si>
@@ -86,13 +80,43 @@
   </si>
   <si>
     <t>n/a</t>
+  </si>
+  <si>
+    <r>
+      <t>C1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>a</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +259,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -1034,17 +1065,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F44852F6-A395-487A-89DF-6A5E0A6BD1B1}">
   <dimension ref="A1:T21"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.85546875" style="2"/>
+    <col min="1" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="15.05" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -1065,7 +1096,7 @@
       <c r="S1" s="1"/>
       <c r="T1"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="17.05" x14ac:dyDescent="0.3">
       <c r="A2" s="13"/>
       <c r="B2" s="4" t="s">
         <v>12</v>
@@ -1086,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>1</v>
@@ -1123,7 +1154,7 @@
       </c>
       <c r="T2"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="15.05" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -1137,7 +1168,7 @@
       <c r="I3" s="5"/>
       <c r="T3"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -1162,7 +1193,7 @@
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -1189,7 +1220,7 @@
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
@@ -1218,7 +1249,7 @@
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
@@ -1249,7 +1280,7 @@
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>0</v>
       </c>
@@ -1282,9 +1313,9 @@
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="17.05" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B9" s="9">
         <v>1.44993697214308E-2</v>
@@ -1293,10 +1324,10 @@
         <v>3.71920598817959E-3</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F9" s="9">
         <v>1.61195282631913E-2</v>
@@ -1317,12 +1348,12 @@
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="17.05" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" s="6">
         <v>2.9987298404739E-3</v>
@@ -1334,10 +1365,10 @@
         <v>2.0616626045377499E-2</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H10" s="9">
         <v>1.48529328040458E-2</v>
@@ -1354,7 +1385,7 @@
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
@@ -1393,7 +1424,7 @@
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
@@ -1434,7 +1465,7 @@
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
@@ -1477,7 +1508,7 @@
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
@@ -1522,7 +1553,7 @@
       <c r="R14" s="10"/>
       <c r="S14" s="10"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
@@ -1569,7 +1600,7 @@
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -1618,7 +1649,7 @@
       <c r="R16" s="10"/>
       <c r="S16" s="10"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -1669,7 +1700,7 @@
       <c r="R17" s="10"/>
       <c r="S17" s="10"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>8</v>
       </c>
@@ -1722,7 +1753,7 @@
       <c r="R18" s="10"/>
       <c r="S18" s="10"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -1777,7 +1808,7 @@
       <c r="R19" s="10"/>
       <c r="S19" s="10"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>10</v>
       </c>
@@ -1834,7 +1865,7 @@
       </c>
       <c r="S20" s="10"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>11</v>
       </c>
